--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.8502996850586</v>
+        <v>10.53817369882202</v>
       </c>
       <c r="D2" t="n">
-        <v>65.8723700635762</v>
+        <v>10.70426013533113</v>
       </c>
       <c r="E2" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F2" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.88211152612521</v>
+        <v>10.05584312299535</v>
       </c>
       <c r="D3" t="n">
-        <v>62.2632410896824</v>
+        <v>10.11777667707339</v>
       </c>
       <c r="E3" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F3" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.68897229363925</v>
+        <v>5.149457997716379</v>
       </c>
       <c r="D4" t="n">
-        <v>32.12556821319895</v>
+        <v>5.22040483464483</v>
       </c>
       <c r="E4" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F4" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.85740950452661</v>
+        <v>6.639329044485575</v>
       </c>
       <c r="D5" t="n">
-        <v>41.15213064606471</v>
+        <v>6.687221229985516</v>
       </c>
       <c r="E5" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F5" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.31045085102202</v>
+        <v>6.550448263291078</v>
       </c>
       <c r="D6" t="n">
-        <v>41.45557045531292</v>
+        <v>6.736530198988349</v>
       </c>
       <c r="E6" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F6" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.81258788661965</v>
+        <v>2.407045531575694</v>
       </c>
       <c r="D7" t="n">
-        <v>15.28146418094983</v>
+        <v>2.483237929404348</v>
       </c>
       <c r="E7" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F7" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.0223650801079</v>
+        <v>5.528634325517534</v>
       </c>
       <c r="D8" t="n">
-        <v>32.40905203838111</v>
+        <v>5.266470956236931</v>
       </c>
       <c r="E8" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F8" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.91697029471458</v>
+        <v>3.72400767289112</v>
       </c>
       <c r="D9" t="n">
-        <v>22.06005936513932</v>
+        <v>3.58475964683514</v>
       </c>
       <c r="E9" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F9" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>10.11101072353895</v>
+        <v>1.64303924257508</v>
       </c>
       <c r="D10" t="n">
-        <v>8.201920000148311</v>
+        <v>1.332812000024101</v>
       </c>
       <c r="E10" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F10" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.87499600317835</v>
+        <v>6.967186850516481</v>
       </c>
       <c r="D11" t="n">
-        <v>39.9492656737279</v>
+        <v>6.491755671980784</v>
       </c>
       <c r="E11" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F11" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95817040209587</v>
+        <v>4.05570269034058</v>
       </c>
       <c r="D12" t="n">
-        <v>28.12360354052121</v>
+        <v>4.570085575334697</v>
       </c>
       <c r="E12" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F12" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.24941765718327</v>
+        <v>5.565530369292282</v>
       </c>
       <c r="D13" t="n">
-        <v>34.66945500162535</v>
+        <v>5.63378643776412</v>
       </c>
       <c r="E13" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F13" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>45.33824799628921</v>
+        <v>7.367465299396997</v>
       </c>
       <c r="D14" t="n">
-        <v>44.82178301922877</v>
+        <v>7.283539740624675</v>
       </c>
       <c r="E14" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F14" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>45.93173121122263</v>
+        <v>7.463906321823679</v>
       </c>
       <c r="D15" t="n">
-        <v>45.37729201489925</v>
+        <v>7.373809952421128</v>
       </c>
       <c r="E15" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F15" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>57.48113705497749</v>
+        <v>9.340684771433843</v>
       </c>
       <c r="D16" t="n">
-        <v>57.85104880636775</v>
+        <v>9.40079543103476</v>
       </c>
       <c r="E16" t="n">
-        <v>15.50751951715075</v>
+        <v>2.519971921536997</v>
       </c>
       <c r="F16" t="n">
-        <v>15.74514659104518</v>
+        <v>2.558586321044842</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
